--- a/data/trans_dic/P32E$calle_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,46</t>
+          <t>0,0; 31,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,88</t>
+          <t>0,0; 81,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,24</t>
+          <t>0,0; 35,19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,67</t>
+          <t>0,0; 44,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,06</t>
+          <t>0,0; 49,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 32,31</t>
+          <t>3,75; 34,21</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,95</t>
+          <t>0,0; 19,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,21</t>
+          <t>0,0; 16,71</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,98</t>
+          <t>0,0; 21,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,8</t>
+          <t>0,0; 17,46</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,56; 65,43</t>
+          <t>26,2; 65,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 64,87</t>
+          <t>11,85; 67,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,05; 61,99</t>
+          <t>28,36; 60,88</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,23</t>
+          <t>0,0; 48,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 61,6</t>
+          <t>4,96; 56,03</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 27,73</t>
+          <t>11,49; 26,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 26,9</t>
+          <t>6,67; 27,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 24,32</t>
+          <t>11,93; 24,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6425</t>
+          <t>0; 5963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5099</t>
+          <t>0; 5100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9214</t>
+          <t>0; 8947</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6503</t>
+          <t>0; 6015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5587</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1018; 8165</t>
+          <t>949; 8644</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5551</t>
+          <t>0; 5817</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 672</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5418</t>
+          <t>0; 5262</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8501</t>
+          <t>0; 8400</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9267</t>
+          <t>0; 8604</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8785; 21642</t>
+          <t>8666; 21621</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>639; 5247</t>
+          <t>959; 5450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11546; 25518</t>
+          <t>11674; 25062</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 5823</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1033; 11525</t>
+          <t>927; 10483</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16888; 38969</t>
+          <t>16138; 37647</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3306; 13675</t>
+          <t>3392; 13819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22680; 46532</t>
+          <t>22828; 46419</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$calle_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,05</t>
+          <t>0,0; 27,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,9</t>
+          <t>0,0; 78,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,19</t>
+          <t>0,0; 33,53</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,09</t>
+          <t>0,0; 44,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,69</t>
+          <t>0,0; 50,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 34,21</t>
+          <t>4,61; 33,65</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,86</t>
+          <t>0,0; 16,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,71</t>
+          <t>0,0; 15,25</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,72</t>
+          <t>0,0; 19,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,46</t>
+          <t>0,0; 14,58</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,2; 65,37</t>
+          <t>20,96; 58,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,85; 67,38</t>
+          <t>8,27; 68,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,36; 60,88</t>
+          <t>22,61; 55,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,23</t>
+          <t>0,0; 40,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 56,03</t>
+          <t>4,81; 51,2</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 26,79</t>
+          <t>10,73; 25,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 27,19</t>
+          <t>5,91; 24,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,93; 24,26</t>
+          <t>10,99; 22,66</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3018</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5963</t>
+          <t>0; 5678</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5100</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8947</t>
+          <t>0; 9024</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4135</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6015</t>
+          <t>0; 6757</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5776</t>
+          <t>0; 6696</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>949; 8644</t>
+          <t>1323; 9660</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1229</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5817</t>
+          <t>0; 5297</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 5415</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2582</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8400</t>
+          <t>0; 8103</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8604</t>
+          <t>0; 8257</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>19312</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8666; 21621</t>
+          <t>8816; 24412</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>959; 5450</t>
+          <t>699; 5758</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11674; 25062</t>
+          <t>11423; 28072</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>987</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4231</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6637</t>
+          <t>0; 6084</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5823</t>
+          <t>0; 5528</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>927; 10483</t>
+          <t>945; 10053</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>34506</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16138; 37647</t>
+          <t>16922; 39856</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3392; 13819</t>
+          <t>3562; 14887</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22828; 46419</t>
+          <t>23942; 49375</t>
         </is>
       </c>
     </row>
